--- a/data/trans_dic/P22$mutaSS-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P22$mutaSS-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Mutualidad de Estado (Seguridad Social)</t>
+          <t>Población que, al menos, es beneficiaria de mutualidades del Estado (Seguridad Social) (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,53</t>
+          <t>1,84; 4,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,07</t>
+          <t>1,49; 4,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,83</t>
+          <t>1,29; 3,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,83</t>
+          <t>0,93; 2,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,32</t>
+          <t>2,4; 5,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,97</t>
+          <t>0,41; 1,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,96</t>
+          <t>0,36; 2,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,97</t>
+          <t>0,8; 2,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,35</t>
+          <t>2,43; 4,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,58</t>
+          <t>1,11; 2,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,49</t>
+          <t>1,05; 2,57</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,21</t>
+          <t>1,0; 2,13</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,26</t>
+          <t>1,96; 4,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,18</t>
+          <t>1,27; 3,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,1</t>
+          <t>1,95; 4,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,31</t>
+          <t>0,88; 3,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,16</t>
+          <t>2,0; 4,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,93</t>
+          <t>1,14; 2,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,6</t>
+          <t>0,39; 1,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,45</t>
+          <t>1,86; 3,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,85</t>
+          <t>2,26; 3,95</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,77</t>
+          <t>1,39; 2,76</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,53</t>
+          <t>1,32; 2,65</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,97</t>
+          <t>1,52; 3,01</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,27</t>
+          <t>1,72; 4,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,55</t>
+          <t>1,33; 3,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,87</t>
+          <t>0,41; 1,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 7,15</t>
+          <t>2,56; 6,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,53</t>
+          <t>1,95; 4,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,85</t>
+          <t>1,39; 3,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,54</t>
+          <t>0,77; 2,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,97</t>
+          <t>0,51; 2,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,82</t>
+          <t>2,06; 3,88</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,32</t>
+          <t>1,59; 3,29</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,92</t>
+          <t>0,72; 1,86</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,83</t>
+          <t>1,58; 3,8</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,03; 6,8</t>
+          <t>4,1; 6,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,25</t>
+          <t>2,56; 5,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,01</t>
+          <t>1,73; 3,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,03</t>
+          <t>1,8; 3,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,66; 4,96</t>
+          <t>2,61; 5,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,18</t>
+          <t>1,89; 4,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,91</t>
+          <t>1,07; 2,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,66</t>
+          <t>1,08; 2,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,64; 5,61</t>
+          <t>3,58; 5,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 4,12</t>
+          <t>2,51; 4,16</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,99</t>
+          <t>1,6; 3,03</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,85</t>
+          <t>1,59; 2,76</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,97; 4,3</t>
+          <t>2,98; 4,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,28</t>
+          <t>2,13; 3,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,85</t>
+          <t>1,75; 2,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,36</t>
+          <t>1,96; 3,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,79; 4,04</t>
+          <t>2,75; 4,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,63</t>
+          <t>1,59; 2,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,75</t>
+          <t>0,97; 1,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,11</t>
+          <t>1,31; 2,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,01; 3,99</t>
+          <t>3,03; 3,96</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 2,79</t>
+          <t>2,0; 2,77</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,14</t>
+          <t>1,47; 2,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 2,54</t>
+          <t>1,78; 2,53</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Mutualidad de Estado (Seguridad Social)</t>
+          <t>Población que, al menos, es beneficiaria de mutualidades del Estado (Seguridad Social) (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12397; 31332</t>
+          <t>12742; 31015</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10466; 28629</t>
+          <t>10466; 28884</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9004; 25788</t>
+          <t>8710; 25013</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5619; 17975</t>
+          <t>5898; 17905</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17143; 36543</t>
+          <t>16493; 35989</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2885; 13738</t>
+          <t>2878; 13084</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2411; 13159</t>
+          <t>2439; 13775</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5588; 13336</t>
+          <t>5432; 13588</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33319; 60045</t>
+          <t>33502; 59973</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15760; 36069</t>
+          <t>15497; 36807</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12756; 33469</t>
+          <t>14175; 34564</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13269; 28953</t>
+          <t>13129; 27980</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18563; 40885</t>
+          <t>18880; 42564</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12822; 32383</t>
+          <t>12886; 33574</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19883; 41884</t>
+          <t>19942; 42451</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12084; 39510</t>
+          <t>10499; 37635</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19216; 40294</t>
+          <t>19335; 40732</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11731; 30285</t>
+          <t>11722; 29211</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4270; 16616</t>
+          <t>4072; 16570</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17638; 33014</t>
+          <t>17841; 33846</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>43339; 74280</t>
+          <t>43588; 76179</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27263; 56673</t>
+          <t>28532; 56487</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27601; 52135</t>
+          <t>27325; 54579</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31144; 63868</t>
+          <t>32763; 64749</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10729; 28921</t>
+          <t>11643; 29870</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9017; 26881</t>
+          <t>10040; 28970</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3035; 14134</t>
+          <t>3077; 14228</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19646; 50409</t>
+          <t>18074; 48018</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13324; 31001</t>
+          <t>13306; 31198</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10066; 29914</t>
+          <t>10815; 29885</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5912; 19849</t>
+          <t>6049; 21143</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5007; 18391</t>
+          <t>4784; 18798</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28442; 51983</t>
+          <t>28055; 52835</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24556; 50882</t>
+          <t>24466; 50426</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11637; 29569</t>
+          <t>11080; 28663</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25422; 62796</t>
+          <t>25874; 62279</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37835; 63891</t>
+          <t>38504; 65510</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23972; 49746</t>
+          <t>24287; 48803</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16380; 37538</t>
+          <t>16246; 37117</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17760; 37333</t>
+          <t>16685; 34830</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27570; 51426</t>
+          <t>27049; 52445</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20164; 43942</t>
+          <t>19895; 43522</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11429; 30369</t>
+          <t>11124; 30648</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11557; 29019</t>
+          <t>11767; 28405</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71886; 110849</t>
+          <t>70865; 106440</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>50348; 82476</t>
+          <t>50105; 83234</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32366; 59161</t>
+          <t>31782; 60065</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>32433; 57558</t>
+          <t>32055; 55755</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>97240; 140671</t>
+          <t>97585; 139614</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>73191; 112473</t>
+          <t>72908; 111940</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>60680; 96571</t>
+          <t>59381; 95608</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>70274; 116316</t>
+          <t>67672; 116004</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>94062; 136296</t>
+          <t>92763; 135492</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>56292; 93592</t>
+          <t>56535; 91782</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33448; 61918</t>
+          <t>34357; 63040</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>48184; 77324</t>
+          <t>47796; 77505</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>200172; 265303</t>
+          <t>201647; 263294</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>139526; 194698</t>
+          <t>139820; 193417</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>103529; 148426</t>
+          <t>101890; 146255</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>126393; 180810</t>
+          <t>126820; 180417</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$mutaSS-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P22$mutaSS-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,48</t>
+          <t>1,74; 4,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,11</t>
+          <t>1,5; 3,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,71</t>
+          <t>1,31; 3,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,82</t>
+          <t>0,82; 2,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,23</t>
+          <t>2,44; 5,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,88</t>
+          <t>0,43; 1,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,05</t>
+          <t>0,37; 2,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,01</t>
+          <t>0,77; 1,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,35</t>
+          <t>2,46; 4,42</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,63</t>
+          <t>1,11; 2,6</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,57</t>
+          <t>1,0; 2,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,13</t>
+          <t>0,95; 2,01</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,43</t>
+          <t>1,9; 4,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,3</t>
+          <t>1,28; 3,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,16</t>
+          <t>1,88; 4,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,15</t>
+          <t>1,56; 3,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,21</t>
+          <t>1,99; 4,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,83</t>
+          <t>1,15; 2,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,59</t>
+          <t>0,47; 1,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,53</t>
+          <t>1,73; 3,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,95</t>
+          <t>2,27; 3,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,76</t>
+          <t>1,44; 2,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,65</t>
+          <t>1,34; 2,65</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,01</t>
+          <t>1,81; 3,07</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,41</t>
+          <t>1,64; 4,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,82</t>
+          <t>1,42; 3,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,88</t>
+          <t>0,4; 1,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,56; 6,81</t>
+          <t>2,54; 6,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,56</t>
+          <t>1,86; 4,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,85</t>
+          <t>1,36; 3,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,71</t>
+          <t>0,8; 2,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,01</t>
+          <t>0,96; 2,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 3,88</t>
+          <t>2,1; 3,9</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,29</t>
+          <t>1,59; 3,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,86</t>
+          <t>0,76; 1,9</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,8</t>
+          <t>1,95; 3,77</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,1; 6,97</t>
+          <t>4,1; 6,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,15</t>
+          <t>2,56; 5,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,96</t>
+          <t>1,76; 3,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,76</t>
+          <t>1,68; 3,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,61; 5,06</t>
+          <t>2,57; 5,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,14</t>
+          <t>1,94; 4,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,94</t>
+          <t>1,06; 2,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,6</t>
+          <t>1,0; 2,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,58; 5,38</t>
+          <t>3,66; 5,43</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 4,16</t>
+          <t>2,48; 4,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,03</t>
+          <t>1,58; 2,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,76</t>
+          <t>1,52; 2,57</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,98; 4,27</t>
+          <t>2,95; 4,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,27</t>
+          <t>2,07; 3,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,82</t>
+          <t>1,82; 2,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,35</t>
+          <t>2,08; 3,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,75; 4,01</t>
+          <t>2,74; 3,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,58</t>
+          <t>1,61; 2,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,78</t>
+          <t>0,93; 1,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,12</t>
+          <t>1,42; 2,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,03; 3,96</t>
+          <t>2,98; 3,93</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 2,77</t>
+          <t>2,02; 2,75</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,11</t>
+          <t>1,49; 2,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 2,53</t>
+          <t>1,86; 2,51</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10555</t>
+          <t>10881</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>9165</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19413</t>
+          <t>20046</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12742; 31015</t>
+          <t>12035; 29622</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10466; 28884</t>
+          <t>10573; 28005</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8710; 25013</t>
+          <t>8831; 25800</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5898; 17905</t>
+          <t>5670; 18764</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16493; 35989</t>
+          <t>16807; 36139</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2878; 13084</t>
+          <t>2988; 13292</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2439; 13775</t>
+          <t>2517; 13911</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5432; 13588</t>
+          <t>5644; 13539</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33502; 59973</t>
+          <t>33933; 60997</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15497; 36807</t>
+          <t>15596; 36365</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14175; 34564</t>
+          <t>13476; 33638</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13129; 27980</t>
+          <t>13547; 28676</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24518</t>
+          <t>25103</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24410</t>
+          <t>26109</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>48928</t>
+          <t>51212</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18880; 42564</t>
+          <t>18214; 41723</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12886; 33574</t>
+          <t>13064; 33115</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19942; 42451</t>
+          <t>19221; 42866</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10499; 37635</t>
+          <t>16414; 37927</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19335; 40732</t>
+          <t>19226; 41213</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11722; 29211</t>
+          <t>11895; 28919</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4072; 16570</t>
+          <t>4870; 17386</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17841; 33846</t>
+          <t>18563; 35207</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>43588; 76179</t>
+          <t>43714; 75888</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28532; 56487</t>
+          <t>29505; 55579</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27325; 54579</t>
+          <t>27728; 54628</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32763; 64749</t>
+          <t>38301; 65090</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31358</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11155</t>
+          <t>12758</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>42513</t>
+          <t>44358</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11643; 29870</t>
+          <t>11099; 29491</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10040; 28970</t>
+          <t>10736; 29902</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3077; 14228</t>
+          <t>3060; 14264</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18074; 48018</t>
+          <t>20387; 48308</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13306; 31198</t>
+          <t>12744; 32254</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10815; 29885</t>
+          <t>10578; 30789</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6049; 21143</t>
+          <t>6229; 19593</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4784; 18798</t>
+          <t>7758; 20071</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28055; 52835</t>
+          <t>28645; 53090</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24466; 50426</t>
+          <t>24414; 50873</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11080; 28663</t>
+          <t>11720; 29208</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25874; 62279</t>
+          <t>31520; 60975</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24718</t>
+          <t>25001</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>18316</t>
+          <t>16447</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>43034</t>
+          <t>41448</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>38504; 65510</t>
+          <t>38531; 64927</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24287; 48803</t>
+          <t>24228; 47703</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16246; 37117</t>
+          <t>16458; 36326</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16685; 34830</t>
+          <t>16670; 34637</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27049; 52445</t>
+          <t>26702; 52647</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19895; 43522</t>
+          <t>20420; 44401</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11124; 30648</t>
+          <t>11098; 30643</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11767; 28405</t>
+          <t>11144; 23826</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>70865; 106440</t>
+          <t>72368; 107415</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>50105; 83234</t>
+          <t>49547; 81436</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31782; 60065</t>
+          <t>31326; 58849</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>32055; 55755</t>
+          <t>32113; 54087</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>91149</t>
+          <t>92585</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>62739</t>
+          <t>64478</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>153888</t>
+          <t>157063</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>97585; 139614</t>
+          <t>96485; 139565</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>72908; 111940</t>
+          <t>70853; 113194</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59381; 95608</t>
+          <t>61598; 97527</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>67672; 116004</t>
+          <t>73559; 117256</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>92763; 135492</t>
+          <t>92490; 134696</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>56535; 91782</t>
+          <t>57404; 91307</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34357; 63040</t>
+          <t>32986; 61015</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>47796; 77505</t>
+          <t>52833; 77940</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>201647; 263294</t>
+          <t>198013; 261137</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>139820; 193417</t>
+          <t>141231; 191928</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>101890; 146255</t>
+          <t>103000; 146308</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>126820; 180417</t>
+          <t>135170; 182247</t>
         </is>
       </c>
     </row>
